--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/ARIZONA_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/ARIZONA_2021.xlsx
@@ -3228,7 +3228,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C160">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C204">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C326">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C335">
@@ -15702,7 +15702,7 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C853">
@@ -15720,7 +15720,7 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C854">
@@ -21541,7 +21541,7 @@
         <v>197</v>
       </c>
       <c r="D1177">
-        <v>0.009709694908571147</v>
+        <v>0.009709694908571148</v>
       </c>
     </row>
     <row r="1178">
